--- a/outputs/daily/hr_rankings_2026-10-01_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01_full.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1292,7 +1300,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2100,8 +2112,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2391,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2416,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2529,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,12 +2564,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2559,101 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2667,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -2692,31 +2720,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2805,12 +2829,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2844,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2859,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3204,8 +3232,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3480,8 +3512,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3756,8 +3792,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -3776,7 +3820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4400,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4461,22 +4509,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4624,31 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -4875,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4900,31 +4960,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5412,8 +5472,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5688,8 +5752,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>47.8</v>
       </c>
       <c r="R2" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.4</v>
+        <v>61.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>47.8</v>
       </c>
       <c r="R3" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6586,7 +6666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>47.8</v>
       </c>
       <c r="R4" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -6862,7 +6946,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +6966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>47.8</v>
       </c>
       <c r="R5" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>55.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7394,8 +7478,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>47.8</v>
       </c>
       <c r="R7" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7685,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7710,31 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>49.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>32.5</v>
+        <v>24</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7823,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,12 +7930,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7853,101 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -7961,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -7986,31 +8086,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>48.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8099,12 +8195,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8210,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8225,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8498,8 +8598,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8774,8 +8878,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>42.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9050,8 +9158,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9070,7 +9186,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>47.8</v>
       </c>
       <c r="R13" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>27.39</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9766,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>35.6</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9755,22 +9875,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9918,31 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10169,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -10194,31 +10326,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>38.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>27.39</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10706,8 +10838,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Truist Park</t>
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>30.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10982,8 +11118,16 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Truist Park</t>
